--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N98_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N98_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.48426757369405</v>
+        <v>6.253693480725283</v>
       </c>
       <c r="D2" t="n">
-        <v>29.994745929958</v>
+        <v>4.874146213618174</v>
       </c>
       <c r="E2" t="n">
-        <v>14.46349838418391</v>
+        <v>2.350318487429885</v>
       </c>
       <c r="F2" t="n">
-        <v>14.96597018865138</v>
+        <v>2.431970155655851</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.36424741748535</v>
+        <v>5.096690205341369</v>
       </c>
       <c r="D3" t="n">
-        <v>12.22884916663985</v>
+        <v>1.987187989578975</v>
       </c>
       <c r="E3" t="n">
-        <v>14.46349838418391</v>
+        <v>2.350318487429885</v>
       </c>
       <c r="F3" t="n">
-        <v>14.96597018865138</v>
+        <v>2.431970155655851</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.16387579306502</v>
+        <v>3.439129816373065</v>
       </c>
       <c r="D4" t="n">
-        <v>21.29732534502001</v>
+        <v>3.460815368565751</v>
       </c>
       <c r="E4" t="n">
-        <v>14.46349838418391</v>
+        <v>2.350318487429885</v>
       </c>
       <c r="F4" t="n">
-        <v>14.96597018865138</v>
+        <v>2.431970155655851</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.71169859418547</v>
+        <v>4.17815102155514</v>
       </c>
       <c r="D5" t="n">
-        <v>15.06785628466178</v>
+        <v>2.448526646257539</v>
       </c>
       <c r="E5" t="n">
-        <v>14.46349838418391</v>
+        <v>2.350318487429885</v>
       </c>
       <c r="F5" t="n">
-        <v>14.96597018865138</v>
+        <v>2.431970155655851</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.09429875386147</v>
+        <v>7.652823547502489</v>
       </c>
       <c r="D6" t="n">
-        <v>23.19737117606921</v>
+        <v>3.769572816111248</v>
       </c>
       <c r="E6" t="n">
-        <v>14.46349838418391</v>
+        <v>2.350318487429885</v>
       </c>
       <c r="F6" t="n">
-        <v>14.96597018865138</v>
+        <v>2.431970155655851</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>8.726318924684595</v>
+        <v>1.418026825261247</v>
       </c>
       <c r="D7" t="n">
-        <v>8.944271909999159</v>
+        <v>1.453444185374863</v>
       </c>
       <c r="E7" t="n">
-        <v>14.46349838418391</v>
+        <v>2.350318487429885</v>
       </c>
       <c r="F7" t="n">
-        <v>14.96597018865138</v>
+        <v>2.431970155655851</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>15.85168009634207</v>
+        <v>2.575898015655587</v>
       </c>
       <c r="D8" t="n">
-        <v>15.93995255850963</v>
+        <v>2.590242290757815</v>
       </c>
       <c r="E8" t="n">
-        <v>14.46349838418391</v>
+        <v>2.350318487429885</v>
       </c>
       <c r="F8" t="n">
-        <v>14.96597018865138</v>
+        <v>2.431970155655851</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>38.57890583348161</v>
+        <v>6.269072197940762</v>
       </c>
       <c r="D9" t="n">
-        <v>38.73306081372863</v>
+        <v>6.294122382230902</v>
       </c>
       <c r="E9" t="n">
-        <v>14.46349838418391</v>
+        <v>2.350318487429885</v>
       </c>
       <c r="F9" t="n">
-        <v>14.96597018865138</v>
+        <v>2.431970155655851</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>47.37544500402067</v>
+        <v>7.698509813153359</v>
       </c>
       <c r="D10" t="n">
-        <v>42.05758307509914</v>
+        <v>6.83435724970361</v>
       </c>
       <c r="E10" t="n">
-        <v>14.46349838418391</v>
+        <v>2.350318487429885</v>
       </c>
       <c r="F10" t="n">
-        <v>14.96597018865138</v>
+        <v>2.431970155655851</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.09722607065306</v>
+        <v>6.353299236481122</v>
       </c>
       <c r="D11" t="n">
-        <v>39.11521443121589</v>
+        <v>6.356222345072582</v>
       </c>
       <c r="E11" t="n">
-        <v>14.46349838418391</v>
+        <v>2.350318487429885</v>
       </c>
       <c r="F11" t="n">
-        <v>14.96597018865138</v>
+        <v>2.431970155655851</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>59.98461634061573</v>
+        <v>9.747500155350057</v>
       </c>
       <c r="D12" t="n">
-        <v>60.11031525453847</v>
+        <v>9.767926228862502</v>
       </c>
       <c r="E12" t="n">
-        <v>14.46349838418391</v>
+        <v>2.350318487429885</v>
       </c>
       <c r="F12" t="n">
-        <v>14.96597018865138</v>
+        <v>2.431970155655851</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
